--- a/stories/arbres/ATOM-SEC.ADU.002-03.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Pablo va au magasin avec maman. Maman est l'accompagnant. Pablo aime rester avec l'accompagnant. Il marche à côté de maman. Maman tient la main. Les pieds de Pablo restent près. Ils voient des poires. Pablo reste avec l'accompagnant. L'adulte connu est là. Maman dit : tu restes avec moi. Pablo hoche la tête. Il sent la main. La main est douce. Plus tard, ils vont à la gare. Le train fait un bruit doux. Pablo se souvient. Il reste avec l'accompagnant. Il reste à côté de maman. Les pieds restent près. La main de maman est là. Maman dit : tu restes avec l'adulte connu. Pablo sourit. Même leçon, autre lieu. L'accompagnant de la famille est là.</t>
+          <t>Pablo va au magasin avec maman. Maman est l'accompagnant. Pablo aime rester avec l'accompagnant. Il marche à côté de maman. Maman tient la main. Les pieds de Pablo restent près. Ils voient des poires. Pablo reste avec l'accompagnant. L'adulte connu est là. Tu restes avec moi. Pablo hoche la tête. Il sent la main. La main est douce. Plus tard, ils vont à la gare. Le train fait un bruit doux. Pablo se souvient. Il reste avec l'accompagnant. Il reste à côté de maman. Les pieds restent près. La main de maman est là. Tu restes avec l'adulte connu. Pablo sourit. Même leçon, autre lieu. L'accompagnant de la famille est là.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Pablo va au magasin avec maman. Maman est l'accompagnant. Pablo aime rester avec l'accompagnant. Il marche à côté de maman. Maman tient la main. Les pieds de Pablo restent près. Ils voient des poires. Pablo reste avec l'accompagnant. L'adulte connu est là.
+maman|Tu restes avec moi.
+narrateur|Pablo hoche la tête. Il sent la main. La main est douce. Plus tard, ils vont à la gare. Le train fait un bruit doux. Pablo se souvient. Il reste avec l'accompagnant. Il reste à côté de maman. Les pieds restent près. La main de maman est là.
+maman|Tu restes avec l'adulte connu.
+narrateur|Pablo sourit. Même leçon, autre lieu. L'accompagnant de la famille est là.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Pablo est au magasin, puis à la gare. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Pablo reste avec maman. Au magasin, puis à la gare. L'adulte connu est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1834,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Pablo et maman prennent le train. Ils restent ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2001,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.002-03.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Pablo sourit. Même leçon, autre lieu. L'accompagnant de la famille est là.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Pablo est au magasin, puis à la gare. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Pablo reste avec maman. Au magasin, puis à la gare. L'adulte connu est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1847,7 @@
           <t>narrateur|Pablo et maman prennent le train. Ils restent ensemble.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.ADU.002-03.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pablo reste avec maman, deux lieux</t>
+          <t>Le bip et le banc d'Aniss</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La caisse bippe. Aniss reste avec maman au magasin, puis à la gare, près du banc.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Pablo va au magasin avec maman. Maman est l'accompagnant. Pablo aime rester avec l'accompagnant. Il marche à côté de maman. Maman tient la main. Les pieds de Pablo restent près. Ils voient des poires. Pablo reste avec l'accompagnant. L'adulte connu est là. Tu restes avec moi. Pablo hoche la tête. Il sent la main. La main est douce. Plus tard, ils vont à la gare. Le train fait un bruit doux. Pablo se souvient. Il reste avec l'accompagnant. Il reste à côté de maman. Les pieds restent près. La main de maman est là. Tu restes avec l'adulte connu. Pablo sourit. Même leçon, autre lieu. L'accompagnant de la famille est là.</t>
+          <t>La caisse fait un petit bip, tout net. Le sac en papier craque entre les doigts. Une poire jaune brille sous la lumière. Le sol du magasin est froid et lisse. Un ticket sort, tout fin, tout chaud. Aniss vit avec papa et maman. En ce moment, Aniss va au magasin avec maman. Maman est l'accompagnant. Aniss aime rester avec l'accompagnant. Il marche à côté de maman. Maman tient la main. Les pieds d'Aniss restent près. Ils voient des poires. Elles sont jaunes, maman. Oui. Tu restes avec moi. Aniss reste avec l'accompagnant. L'adulte connu est là. Aniss hoche la tête. Il sent la main. La main est douce. Bravo. Tu restes à côté. Tu as fait du bon travail. Maman glisse le ticket dans sa poche. Le ticket est encore un peu chaud. Plus tard, ils vont à la gare. Le quai sent un peu le vent. Une horloge fait un petit tic. Le train fait un bruit doux, très bas. Un banc est froid sous les mains. Une feuille sèche court sur le quai. On s'assoit un moment ? Oui. Aniss s'assoit près de maman. Aniss se souvient. Il reste avec l'accompagnant. Il reste à côté de maman. Les pieds restent près du banc. La main de maman tient encore. Je reste avec toi. Tu restes avec l'adulte connu. Bravo, Aniss. Aniss sourit. Ici aussi, Aniss reste près de maman. L'accompagnant de la famille reste près. Le sac craque encore un peu, plein de poires.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,53 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Pablo va au magasin avec maman. Maman est l'accompagnant. Pablo aime rester avec l'accompagnant. Il marche à côté de maman. Maman tient la main. Les pieds de Pablo restent près. Ils voient des poires. Pablo reste avec l'accompagnant. L'adulte connu est là.
+          <t>narrateur|La caisse fait un petit bip, tout net.
+narrateur|Le sac en papier craque entre les doigts.
+narrateur|Une poire jaune brille sous la lumière.
+narrateur|Le sol du magasin est froid et lisse.
+narrateur|Un ticket sort, tout fin, tout chaud.
+narrateur|Aniss vit avec papa et maman.
+narrateur|En ce moment, Aniss va au magasin avec maman.
+narrateur|Maman est l'accompagnant.
+narrateur|Aniss aime rester avec l'accompagnant.
+narrateur|Il marche à côté de maman.
+narrateur|Maman tient la main.
+narrateur|Les pieds d'Aniss restent près.
+narrateur|Ils voient des poires.
+enfant-m|Elles sont jaunes, maman.
+maman|Oui.
 maman|Tu restes avec moi.
-narrateur|Pablo hoche la tête. Il sent la main. La main est douce. Plus tard, ils vont à la gare. Le train fait un bruit doux. Pablo se souvient. Il reste avec l'accompagnant. Il reste à côté de maman. Les pieds restent près. La main de maman est là.
+narrateur|Aniss reste avec l'accompagnant.
+narrateur|L'adulte connu est là.
+narrateur|Aniss hoche la tête.
+narrateur|Il sent la main.
+narrateur|La main est douce.
+maman|Bravo.
+maman|Tu restes à côté.
+maman|Tu as fait du bon travail.
+narrateur|Maman glisse le ticket dans sa poche.
+narrateur|Le ticket est encore un peu chaud.
+narrateur|Plus tard, ils vont à la gare.
+narrateur|Le quai sent un peu le vent.
+narrateur|Une horloge fait un petit tic.
+narrateur|Le train fait un bruit doux, très bas.
+narrateur|Un banc est froid sous les mains.
+narrateur|Une feuille sèche court sur le quai.
+maman|On s'assoit un moment ?
+enfant-m|Oui.
+narrateur|Aniss s'assoit près de maman.
+narrateur|Aniss se souvient.
+narrateur|Il reste avec l'accompagnant.
+narrateur|Il reste à côté de maman.
+narrateur|Les pieds restent près du banc.
+narrateur|La main de maman tient encore.
+enfant-m|Je reste avec toi.
 maman|Tu restes avec l'adulte connu.
-narrateur|Pablo sourit. Même leçon, autre lieu. L'accompagnant de la famille est là.</t>
+maman|Bravo, Aniss.
+narrateur|Aniss sourit.
+narrateur|Ici aussi, Aniss reste près de maman.
+narrateur|L'accompagnant de la famille reste près.
+narrateur|Le sac craque encore un peu, plein de poires.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1344,7 +1398,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Pablo est au magasin, puis à la gare. Que fait-il ?</t>
+          <t>Aniss est au magasin, puis à la gare. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1558,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Pablo est au magasin, puis à la gare. Que fait-il ?</t>
+          <t>narrateur|Aniss est au magasin, puis à la gare.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1587,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Pablo reste avec maman. Au magasin, puis à la gare. L'adulte connu est là.</t>
+          <t>Aniss reste avec maman. Au magasin, puis à la gare. L'adulte connu est là. Tu restes avec moi ? Oui, maman. Bravo. Tu restes avec l'accompagnant. Le banc est encore un peu froid.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1731,14 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Pablo reste avec maman. Au magasin, puis à la gare. L'adulte connu est là.</t>
+          <t>narrateur|Aniss reste avec maman.
+narrateur|Au magasin, puis à la gare.
+narrateur|L'adulte connu est là.
+maman|Tu restes avec moi ?
+enfant-m|Oui, maman.
+maman|Bravo.
+maman|Tu restes avec l'accompagnant.
+narrateur|Le banc est encore un peu froid.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1766,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Pablo et maman prennent le train. Ils restent ensemble.</t>
+          <t>Papa les rejoint près du banc. Me voici. Tu es avec maman ? Oui, papa. Bravo. Tu restes avec l'adulte connu. Le train s'arrête tout doux. Les portes s'ouvrent tout doux. On monte ensemble. Aniss et maman prennent le train. Ils restent ensemble. Papa s'assoit à côté. La main est tenue ? Oui. Tu as fait du bon travail. Tu as fini, Aniss ? Oui. Le train fait encore son bruit doux. Le sac de poires est posé près des genoux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,7 +1906,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Pablo et maman prennent le train. Ils restent ensemble.</t>
+          <t>narrateur|Papa les rejoint près du banc.
+papa|Me voici.
+papa|Tu es avec maman ?
+enfant-m|Oui, papa.
+papa|Bravo.
+papa|Tu restes avec l'adulte connu.
+narrateur|Le train s'arrête tout doux.
+narrateur|Les portes s'ouvrent tout doux.
+maman|On monte ensemble.
+narrateur|Aniss et maman prennent le train.
+narrateur|Ils restent ensemble.
+narrateur|Papa s'assoit à côté.
+maman|La main est tenue ?
+enfant-m|Oui.
+maman|Tu as fait du bon travail.
+papa|Tu as fini, Aniss ?
+enfant-m|Oui.
+narrateur|Le train fait encore son bruit doux.
+narrateur|Le sac de poires est posé près des genoux.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1872,7 +1952,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Je suis resté avec maman. Bravo. Tu as fait du bon travail. Le train avance tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,7 +2092,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Je suis resté avec maman.
+papa|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le train avance tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2034,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2156,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.002-03.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La caisse fait un petit bip, tout net. Le sac en papier craque entre les doigts. Une poire jaune brille sous la lumière. Le sol du magasin est froid et lisse. Un ticket sort, tout fin, tout chaud. Aniss vit avec papa et maman. En ce moment, Aniss va au magasin avec maman. Maman est l'accompagnant. Aniss aime rester avec l'accompagnant. Il marche à côté de maman. Maman tient la main. Les pieds d'Aniss restent près. Ils voient des poires. Elles sont jaunes, maman. Oui. Tu restes avec moi. Aniss reste avec l'accompagnant. L'adulte connu est là. Aniss hoche la tête. Il sent la main. La main est douce. Bravo. Tu restes à côté. Tu as fait du bon travail. Maman glisse le ticket dans sa poche. Le ticket est encore un peu chaud. Plus tard, ils vont à la gare. Le quai sent un peu le vent. Une horloge fait un petit tic. Le train fait un bruit doux, très bas. Un banc est froid sous les mains. Une feuille sèche court sur le quai. On s'assoit un moment ? Oui. Aniss s'assoit près de maman. Aniss se souvient. Il reste avec l'accompagnant. Il reste à côté de maman. Les pieds restent près du banc. La main de maman tient encore. Je reste avec toi. Tu restes avec l'adulte connu. Bravo, Aniss. Aniss sourit. Ici aussi, Aniss reste près de maman. L'accompagnant de la famille reste près. Le sac craque encore un peu, plein de poires.</t>
+          <t>La caisse fait un petit bip, tout net. Le sac en papier craque entre les doigts. Une poire jaune brille sous la lumière. Le sol du magasin est froid et lisse. Un ticket sort, tout fin, tout chaud. Aniss vit avec papa et maman. En ce moment, Aniss va au magasin avec maman. Maman est l'accompagnant. Aniss aime rester avec l'accompagnant. Il marche à côté de maman. Maman tient la main. Les pieds d'Aniss restent près. Ils voient des poires. Elles sont jaunes, maman. Oui. Tu restes avec moi. Aniss reste avec l'accompagnant. L'adulte connu est là. Aniss hoche la tête. Il sent la main. La main est douce. Bravo. Tu restes à côté. Maman glisse le ticket dans sa poche. Le ticket est encore un peu chaud. Plus tard, ils vont à la gare. Le quai sent un peu le vent. Une horloge fait un petit tic. Le train fait un bruit doux, très bas. Un banc est froid sous les mains. Une feuille sèche court sur le quai. On s'assoit un moment ? Oui. Aniss s'assoit près de maman. Aniss se souvient. Il reste avec l'accompagnant. Il reste à côté de maman. Les pieds restent près du banc. La main de maman tient encore. Je reste avec toi. Tu restes avec l'adulte connu. Bravo, Aniss. Aniss sourit. Ici aussi, Aniss reste près de maman. L'accompagnant de la famille reste près. Le sac craque encore un peu, plein de poires.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Pablo va au magasin avec maman. Maman est l'accompagnant. Pablo aime &lt;emphasis level="moderate"&gt;rester&lt;/emphasis&gt; avec l'accompagnant. Il marche à côté de maman. Maman tient la main. Les pieds de Pablo restent près. Ils voient des poires. Pablo reste avec l'accompagnant. L'adulte connu est là. Maman dit : tu restes avec moi. Pablo hoche la tête. Il sent la main. La main est douce. Plus tard, ils vont à la gare. Le train fait un bruit doux. Pablo se souvient. Il reste avec l'accompagnant. Il reste à côté de maman. Les pieds restent près. La main de maman est là. Maman dit : tu restes avec l'adulte connu. Pablo sourit. Même leçon, autre lieu. L'accompagnant de la famille est là.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La caisse fait un petit bip, tout net. Le sac en papier craque entre les doigts. Une poire jaune brille sous la lumière. Le sol du magasin est froid et lisse. Un ticket sort, tout fin, tout chaud. Aniss vit avec papa et maman. En ce moment, Aniss va au magasin avec maman. Maman est l'accompagnant. Aniss aime rester avec l'accompagnant. Il marche à côté de maman. Maman tient la main. Les pieds d'Aniss restent près. Ils voient des poires. Elles sont jaunes, maman. Oui. Tu restes avec moi. Aniss reste avec l'accompagnant. L'adulte connu est là. Aniss hoche la tête. Il sent la main. La main est douce. Bravo. Tu restes à côté. Maman glisse le ticket dans sa poche. Le ticket est encore un peu chaud. Plus tard, ils vont à la gare. Le quai sent un peu le vent. Une horloge fait un petit tic. Le train fait un bruit doux, très bas. Un banc est froid sous les mains. Une feuille sèche court sur le quai. On s'assoit un moment ? Oui. Aniss s'assoit près de maman. Aniss se souvient. Il reste avec l'accompagnant. Il reste à côté de maman. Les pieds restent près du banc. La main de maman tient encore. Je reste avec toi. Tu restes avec l'adulte connu. Bravo, Aniss. Aniss sourit. Ici aussi, Aniss reste près de maman. L'accompagnant de la famille reste près. Le sac craque encore un peu, plein de poires.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1347,7 +1347,6 @@
 narrateur|La main est douce.
 maman|Bravo.
 maman|Tu restes à côté.
-maman|Tu as fait du bon travail.
 narrateur|Maman glisse le ticket dans sa poche.
 narrateur|Le ticket est encore un peu chaud.
 narrateur|Plus tard, ils vont à la gare.
@@ -1373,7 +1372,6 @@
 narrateur|Le sac craque encore un peu, plein de poires.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1403,7 +1401,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Pablo est au magasin, puis à la gare. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss est au magasin, puis à la gare. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1562,7 +1560,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1592,7 +1589,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Pablo reste avec maman. Au magasin, puis à la gare. L'adulte connu est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss reste avec maman. Au magasin, puis à la gare. L'adulte connu est là. Tu restes avec moi ? Oui, maman. Bravo. Tu restes avec l'accompagnant. Le banc est encore un peu froid.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1741,7 +1738,6 @@
 narrateur|Le banc est encore un peu froid.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1766,12 +1762,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa les rejoint près du banc. Me voici. Tu es avec maman ? Oui, papa. Bravo. Tu restes avec l'adulte connu. Le train s'arrête tout doux. Les portes s'ouvrent tout doux. On monte ensemble. Aniss et maman prennent le train. Ils restent ensemble. Papa s'assoit à côté. La main est tenue ? Oui. Tu as fait du bon travail. Tu as fini, Aniss ? Oui. Le train fait encore son bruit doux. Le sac de poires est posé près des genoux.</t>
+          <t>Papa les rejoint près du banc. Me voici. Tu es avec maman ? Oui, papa. Bravo. Tu restes avec l'adulte connu. Le train s'arrête tout doux. Les portes s'ouvrent tout doux. On monte ensemble. Aniss et maman prennent le train. Ils restent ensemble. Papa s'assoit à côté. La main est tenue ? Oui. Tu as fini, Aniss ? Oui. Le train fait encore son bruit doux. Le sac de poires est posé près des genoux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Pablo et maman prennent le train. Ils restent ensemble.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa les rejoint près du banc. Me voici. Tu es avec maman ? Oui, papa. Bravo. Tu restes avec l'adulte connu. Le train s'arrête tout doux. Les portes s'ouvrent tout doux. On monte ensemble. Aniss et maman prennent le train. Ils restent ensemble. Papa s'assoit à côté. La main est tenue ? Oui. Tu as fini, Aniss ? Oui. Le train fait encore son bruit doux. Le sac de poires est posé près des genoux.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1920,14 +1916,12 @@
 narrateur|Papa s'assoit à côté.
 maman|La main est tenue ?
 enfant-m|Oui.
-maman|Tu as fait du bon travail.
 papa|Tu as fini, Aniss ?
 enfant-m|Oui.
 narrateur|Le train fait encore son bruit doux.
 narrateur|Le sac de poires est posé près des genoux.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1952,12 +1946,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Je suis resté avec maman. Bravo. Tu as fait du bon travail. Le train avance tout doux. L'histoire est finie.</t>
+          <t>Je suis resté avec maman. Bravo. Le train avance tout doux.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je suis resté avec maman. Bravo. Le train avance tout doux.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2094,12 +2088,9 @@
         <is>
           <t>enfant-m|Je suis resté avec maman.
 papa|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le train avance tout doux.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le train avance tout doux.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2118,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2163,6 +2154,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.002-03.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-03.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pablo, maman</t>
+          <t>Aniss, maman, papa</t>
         </is>
       </c>
     </row>
